--- a/Result/profitability/6504.xlsx
+++ b/Result/profitability/6504.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05750000000000004</v>
+        <v>0.009999999999999964</v>
       </c>
       <c r="N2" t="n">
-        <v>13.03</v>
+        <v>13.35125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3149999999999999</v>
+        <v>0.1625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.9075</v>
+        <v>13.89375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.15625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.25875</v>
+        <v>14.41875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2325</v>
+        <v>0.625</v>
       </c>
       <c r="N5" t="n">
-        <v>14.885</v>
+        <v>15.04</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7625</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>15.06875</v>
+        <v>15.0925</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>99.2</v>
@@ -1264,10 +1264,10 @@
         <v>-0.79</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6025</v>
+        <v>0.4587499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>14.83125</v>
+        <v>14.67625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8937,6 +8937,133 @@
       </c>
       <c r="AM67" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1512</v>
+      </c>
+      <c r="E68" t="n">
+        <v>227</v>
+      </c>
+      <c r="F68" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="G68" t="n">
+        <v>32</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1.86%</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>-32</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-0.07250000000000004</v>
+      </c>
+      <c r="N68" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="X68" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>-0.7299999999999986</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-0.05297532656023207</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>-0.9721362229102167</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.1049957662997461</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
